--- a/kit_teste/03_PROPOSTA_ATENCAO.xlsx
+++ b/kit_teste/03_PROPOSTA_ATENCAO.xlsx
@@ -16,10 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
-  </numFmts>
-  <fonts count="9">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,53 +26,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="18"/>
+      <sz val="14"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00555555"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -83,41 +42,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002D5F8A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001A7A4A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -125,127 +54,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -611,20 +428,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H25"/>
+  <dimension ref="A2:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>PROPOSTA COMERCIAL</t>
@@ -632,515 +449,433 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Modernização de Compras — Cenário de teste: ATENÇÃO (variação média)</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Modernização de Compras (SFP) — Cenário de teste: ATENÇÃO (+~23%)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. IDENTIFICAÇÃO</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Fornecedor</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>TechSoft Soluções Ltda.</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>CNPJ</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>12.345.678/0001-90</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Contato</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>João Silva</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Validade</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>30 dias</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. ESCOPO TÉCNICO — CONTAGEM SFP 2.2</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Funcionalidade / Componente</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Operação</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>PF Unit.</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>Qtd</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>PF Total</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>Observação</t>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Obs</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Cadastro de pedido de compra</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cadastrar pedido de compra</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Fluxo de aprovação de pedido</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ItemPedido</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="E12" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="E12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="A13" t="n">
         <v>3</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Consulta de histórico de fornecedores</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>INF</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Aprovar pedido de compra</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
+      <c r="A14" t="n">
         <v>4</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Relatório de gastos por centro de custo</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>AGL</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pedido</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CHG</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="A15" t="n">
         <v>5</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Notificação de vencimento de contrato</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Consultar histórico de fornecedores</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n">
+      <c r="A16" t="n">
         <v>6</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Autenticação e controle de acesso</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HistoricoFornecedor</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="E16" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="E16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Log de auditoria (LGPD)</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Emitir relatório de gastos por centro de custo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="n">
+      <c r="A18" t="n">
         <v>8</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Testes automatizados e deploy CI/CD</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>ALT</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CentroCusto</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CHG</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL DE PONTOS DE FUNÇÃO (PF BRUTOS)</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="18" t="n">
-        <v>95</v>
-      </c>
-      <c r="H19" s="19" t="n"/>
+      <c r="A19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Notificar vencimento de contrato por e-mail</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AgendaNotificacao</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL DE PONTOS DE FUNÇÃO</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. PRECIFICAÇÃO</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Valor R$/PF</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="20" t="n">
+      <c r="C24" t="n">
         <v>820</v>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Total PF</t>
         </is>
       </c>
-      <c r="E22" s="16" t="n">
-        <v>95</v>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="E24" t="n">
+        <v>71</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Valor Total</t>
         </is>
       </c>
-      <c r="G22" s="20" t="n">
-        <v>77900</v>
-      </c>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Prazo de Entrega</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Modalidade</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>Ponto de Função (SFP 2.2)</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>Resumo para Motor APF  |  Total PF: 95  |  R$/PF: R$ 820.00  |  Valor Total: R$ 77,900.00</t>
+      <c r="G24" t="n">
+        <v>58220</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Resumo para Motor APF  |  Total PF: 71  |  R$/PF: R$ 820.00  |  Valor Total: R$ 58,220.00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A22:B22"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>